--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -357,7 +357,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="11.53"/>
@@ -7379,6 +7379,386 @@
       </c>
       <c r="L185" s="3" t="n">
         <v>-37</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="7" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F186" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H186" s="1" t="n">
+        <v>2325</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="7" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F187" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H187" s="1" t="n">
+        <v>2325</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K187" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L187" s="3" t="n">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="7" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F188" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H188" s="1" t="n">
+        <v>1478</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="7" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="F189" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H189" s="1" t="n">
+        <v>1478</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="K189" s="3" t="n">
+        <v>-69</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="7" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F190" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H190" s="1" t="n">
+        <v>1222</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="7" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F191" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H191" s="1" t="n">
+        <v>1222</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="7" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F192" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H192" s="1" t="n">
+        <v>1624</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="7" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F193" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H193" s="1" t="n">
+        <v>1624</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>-91</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="7" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F194" s="1" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="7" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F195" s="1" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>-78.1</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>-26.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -201,7 +201,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -216,10 +216,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -357,10 +353,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="17.47"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.1"/>
@@ -388,7 +386,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -397,7 +395,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -408,10 +406,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="6" t="n">
         <v>45680</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="1" t="n">
@@ -446,10 +444,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="6" t="n">
         <v>45680</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -484,10 +482,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>45685</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="n">
@@ -522,10 +520,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>45685</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -560,10 +558,10 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>45686</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="n">
@@ -598,10 +596,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>45686</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1" t="n">
@@ -636,10 +634,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>45688</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1" t="n">
@@ -674,10 +672,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>45688</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="n">
@@ -712,10 +710,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>45693</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="n">
@@ -750,10 +748,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>45693</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1" t="n">
@@ -788,10 +786,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>45695</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="1" t="n">
@@ -826,10 +824,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>45695</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -864,10 +862,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>45701</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="n">
@@ -902,10 +900,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>45701</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="1" t="n">
@@ -940,10 +938,10 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>45705</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -978,10 +976,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>45705</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="n">
@@ -1016,10 +1014,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>45707</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -1054,10 +1052,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>45707</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -1092,10 +1090,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>45708</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="1" t="n">
@@ -1130,10 +1128,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>45708</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="1" t="n">
@@ -1168,10 +1166,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>45713</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -1206,10 +1204,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>45713</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -1244,10 +1242,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>45715</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="1" t="n">
@@ -1282,10 +1280,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>45715</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="1" t="n">
@@ -1320,10 +1318,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>45716</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="1" t="n">
@@ -1358,10 +1356,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="6" t="n">
         <v>45716</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="1" t="n">
@@ -1396,10 +1394,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="6" t="n">
         <v>45716</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="1" t="n">
@@ -1434,10 +1432,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="6" t="n">
         <v>45716</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="1" t="n">
@@ -1472,10 +1470,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="n">
@@ -1510,10 +1508,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="1" t="n">
@@ -1548,10 +1546,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>45721</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="1" t="n">
@@ -1586,10 +1584,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="6" t="n">
         <v>45721</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="1" t="n">
@@ -1624,10 +1622,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>45722</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="1" t="n">
@@ -1662,10 +1660,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="6" t="n">
         <v>45722</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="1" t="n">
@@ -1700,10 +1698,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="6" t="n">
         <v>45726</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="1" t="n">
@@ -1738,10 +1736,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="6" t="n">
         <v>45726</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="1" t="n">
@@ -1776,10 +1774,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="6" t="n">
         <v>45727</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="1" t="n">
@@ -1814,10 +1812,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="6" t="n">
         <v>45727</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="1" t="n">
@@ -1852,10 +1850,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="6" t="n">
         <v>45728</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="1" t="n">
@@ -1890,10 +1888,10 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="6" t="n">
         <v>45728</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="1" t="n">
@@ -1928,10 +1926,10 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="6" t="n">
         <v>45729</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="1" t="n">
@@ -1966,10 +1964,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="6" t="n">
         <v>45729</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="1" t="n">
@@ -2004,10 +2002,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="6" t="n">
         <v>45733</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="1" t="n">
@@ -2042,10 +2040,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="6" t="n">
         <v>45733</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="1" t="n">
@@ -2080,10 +2078,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="6" t="n">
         <v>45743</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="1" t="n">
@@ -2118,10 +2116,10 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="6" t="n">
         <v>45743</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="1" t="n">
@@ -2156,10 +2154,10 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="6" t="n">
         <v>45744</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="1" t="n">
@@ -2194,10 +2192,10 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="6" t="n">
         <v>45744</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="1" t="n">
@@ -2232,10 +2230,10 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="1" t="n">
@@ -2270,10 +2268,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="1" t="n">
@@ -2308,10 +2306,10 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="6" t="n">
         <v>45750</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="1" t="n">
@@ -2346,10 +2344,10 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="6" t="n">
         <v>45750</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="1" t="n">
@@ -2384,10 +2382,10 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="6" t="n">
         <v>45756</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="1" t="n">
@@ -2422,10 +2420,10 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="6" t="n">
         <v>45756</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="1" t="n">
@@ -2460,10 +2458,10 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="6" t="n">
         <v>45759</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="n">
@@ -2498,10 +2496,10 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="6" t="n">
         <v>45759</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="1" t="n">
@@ -2536,10 +2534,10 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="6" t="n">
         <v>45761</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="1" t="n">
@@ -2574,10 +2572,10 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="6" t="n">
         <v>45761</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C59" s="1" t="n">
@@ -2612,10 +2610,10 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="6" t="n">
         <v>45767</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="1" t="n">
@@ -2650,10 +2648,10 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="6" t="n">
         <v>45767</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="1" t="n">
@@ -2688,10 +2686,10 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="6" t="n">
         <v>45768</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="n">
@@ -2726,10 +2724,10 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="6" t="n">
         <v>45768</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="1" t="n">
@@ -2764,10 +2762,10 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="6" t="n">
         <v>45771</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="1" t="n">
@@ -2802,10 +2800,10 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="6" t="n">
         <v>45771</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C65" s="1" t="n">
@@ -2840,10 +2838,10 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="6" t="n">
         <v>45772</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="1" t="n">
@@ -2878,10 +2876,10 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="6" t="n">
         <v>45772</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="1" t="n">
@@ -2916,10 +2914,10 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="6" t="n">
         <v>45775</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="n">
@@ -2954,10 +2952,10 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="6" t="n">
         <v>45775</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="1" t="n">
@@ -2992,10 +2990,10 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="6" t="n">
         <v>45777</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="1" t="n">
@@ -3030,10 +3028,10 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="6" t="n">
         <v>45777</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="1" t="n">
@@ -3068,10 +3066,10 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="6" t="n">
         <v>45789</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="1" t="n">
@@ -3106,10 +3104,10 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="6" t="n">
         <v>45789</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="1" t="n">
@@ -3144,10 +3142,10 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="6" t="n">
         <v>45804</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C74" s="1" t="n">
@@ -3182,10 +3180,10 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="6" t="n">
         <v>45804</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="1" t="n">
@@ -3220,10 +3218,10 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
+      <c r="A76" s="6" t="n">
         <v>45804</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="1" t="n">
@@ -3258,10 +3256,10 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="6" t="n">
         <v>45804</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="1" t="n">
@@ -3296,10 +3294,10 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
+      <c r="A78" s="6" t="n">
         <v>45814</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="1" t="n">
@@ -3334,10 +3332,10 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="6" t="n">
         <v>45814</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="1" t="n">
@@ -3372,10 +3370,10 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
+      <c r="A80" s="6" t="n">
         <v>45817</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="1" t="n">
@@ -3410,10 +3408,10 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="6" t="n">
         <v>45817</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="1" t="n">
@@ -3448,10 +3446,10 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="n">
+      <c r="A82" s="6" t="n">
         <v>45818</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C82" s="1" t="n">
@@ -3486,10 +3484,10 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="6" t="n">
         <v>45818</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="1" t="n">
@@ -3524,10 +3522,10 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="n">
+      <c r="A84" s="6" t="n">
         <v>45819</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C84" s="1" t="n">
@@ -3562,10 +3560,10 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="6" t="n">
         <v>45819</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="1" t="n">
@@ -3600,10 +3598,10 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="n">
+      <c r="A86" s="6" t="n">
         <v>45823</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C86" s="1" t="n">
@@ -3638,10 +3636,10 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="6" t="n">
         <v>45823</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="1" t="n">
@@ -3676,10 +3674,10 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
+      <c r="A88" s="6" t="n">
         <v>45824</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C88" s="1" t="n">
@@ -3714,10 +3712,10 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="6" t="n">
         <v>45824</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="1" t="n">
@@ -3752,10 +3750,10 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="n">
+      <c r="A90" s="6" t="n">
         <v>45825</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C90" s="1" t="n">
@@ -3790,10 +3788,10 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="6" t="n">
         <v>45825</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="1" t="n">
@@ -3828,10 +3826,10 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="n">
+      <c r="A92" s="6" t="n">
         <v>45833</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="1" t="n">
@@ -3866,10 +3864,10 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="6" t="n">
         <v>45833</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="1" t="n">
@@ -3904,10 +3902,10 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="n">
+      <c r="A94" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C94" s="1" t="n">
@@ -3942,10 +3940,10 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="1" t="n">
@@ -3980,10 +3978,10 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7" t="n">
+      <c r="A96" s="6" t="n">
         <v>45851</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="1" t="n">
@@ -4018,10 +4016,10 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="6" t="n">
         <v>45851</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="1" t="n">
@@ -4056,10 +4054,10 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7" t="n">
+      <c r="A98" s="6" t="n">
         <v>45852</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C98" s="1" t="n">
@@ -4094,10 +4092,10 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="6" t="n">
         <v>45852</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="1" t="n">
@@ -4132,10 +4130,10 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7" t="n">
+      <c r="A100" s="6" t="n">
         <v>45854</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C100" s="1" t="n">
@@ -4170,10 +4168,10 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="6" t="n">
         <v>45854</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="1" t="n">
@@ -4208,10 +4206,10 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="n">
+      <c r="A102" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C102" s="1" t="n">
@@ -4246,10 +4244,10 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="1" t="n">
@@ -4284,10 +4282,10 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="1" t="n">
@@ -4322,10 +4320,10 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C105" s="1" t="n">
@@ -4360,10 +4358,10 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7" t="n">
+      <c r="A106" s="6" t="n">
         <v>45859</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C106" s="1" t="n">
@@ -4398,10 +4396,10 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="6" t="n">
         <v>45859</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C107" s="1" t="n">
@@ -4436,10 +4434,10 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="6" t="n">
         <v>45860</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C108" s="1" t="n">
@@ -4474,10 +4472,10 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="6" t="n">
         <v>45860</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="1" t="n">
@@ -4512,10 +4510,10 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="n">
+      <c r="A110" s="6" t="n">
         <v>45863</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C110" s="1" t="n">
@@ -4550,10 +4548,10 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="6" t="n">
         <v>45863</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="1" t="n">
@@ -4588,10 +4586,10 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7" t="n">
+      <c r="A112" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="1" t="n">
@@ -4626,10 +4624,10 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C113" s="1" t="n">
@@ -4664,10 +4662,10 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="n">
+      <c r="A114" s="6" t="n">
         <v>45894</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C114" s="1" t="n">
@@ -4702,10 +4700,10 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="6" t="n">
         <v>45894</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C115" s="1" t="n">
@@ -4740,10 +4738,10 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7" t="n">
+      <c r="A116" s="6" t="n">
         <v>45895</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C116" s="1" t="n">
@@ -4778,10 +4776,10 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="6" t="n">
         <v>45895</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C117" s="1" t="n">
@@ -4816,10 +4814,10 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7" t="n">
+      <c r="A118" s="6" t="n">
         <v>45898</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C118" s="1" t="n">
@@ -4854,10 +4852,10 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="6" t="n">
         <v>45898</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C119" s="1" t="n">
@@ -4892,10 +4890,10 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7" t="n">
+      <c r="A120" s="6" t="n">
         <v>45905</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C120" s="1" t="n">
@@ -4930,10 +4928,10 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7" t="n">
+      <c r="A121" s="6" t="n">
         <v>45905</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C121" s="1" t="n">
@@ -4968,10 +4966,10 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7" t="n">
+      <c r="A122" s="6" t="n">
         <v>45909</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C122" s="1" t="n">
@@ -5006,10 +5004,10 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="n">
+      <c r="A123" s="6" t="n">
         <v>45909</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C123" s="1" t="n">
@@ -5044,10 +5042,10 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="7" t="n">
+      <c r="A124" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C124" s="1" t="n">
@@ -5082,10 +5080,10 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7" t="n">
+      <c r="A125" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C125" s="1" t="n">
@@ -5120,10 +5118,10 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="7" t="n">
+      <c r="A126" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C126" s="1" t="n">
@@ -5149,10 +5147,10 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7" t="n">
+      <c r="A127" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C127" s="1" t="n">
@@ -5178,10 +5176,10 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7" t="n">
+      <c r="A128" s="6" t="n">
         <v>45921</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C128" s="1" t="n">
@@ -5216,10 +5214,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7" t="n">
+      <c r="A129" s="6" t="n">
         <v>45921</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C129" s="1" t="n">
@@ -5254,10 +5252,10 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7" t="n">
+      <c r="A130" s="6" t="n">
         <v>45922</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C130" s="1" t="n">
@@ -5292,10 +5290,10 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7" t="n">
+      <c r="A131" s="6" t="n">
         <v>45922</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C131" s="1" t="n">
@@ -5330,10 +5328,10 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7" t="n">
+      <c r="A132" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C132" s="1" t="n">
@@ -5368,10 +5366,10 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7" t="n">
+      <c r="A133" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C133" s="1" t="n">
@@ -5406,10 +5404,10 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="7" t="n">
+      <c r="A134" s="6" t="n">
         <v>45927</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C134" s="1" t="n">
@@ -5444,10 +5442,10 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7" t="n">
+      <c r="A135" s="6" t="n">
         <v>45927</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C135" s="1" t="n">
@@ -5482,10 +5480,10 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7" t="n">
+      <c r="A136" s="6" t="n">
         <v>45932</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C136" s="1" t="n">
@@ -5520,10 +5518,10 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7" t="n">
+      <c r="A137" s="6" t="n">
         <v>45932</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C137" s="1" t="n">
@@ -5558,10 +5556,10 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7" t="n">
+      <c r="A138" s="6" t="n">
         <v>45933</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C138" s="1" t="n">
@@ -5596,10 +5594,10 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7" t="n">
+      <c r="A139" s="6" t="n">
         <v>45933</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C139" s="1" t="n">
@@ -5634,10 +5632,10 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7" t="n">
+      <c r="A140" s="6" t="n">
         <v>45938</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C140" s="1" t="n">
@@ -5672,10 +5670,10 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7" t="n">
+      <c r="A141" s="6" t="n">
         <v>45938</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C141" s="1" t="n">
@@ -5710,10 +5708,10 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7" t="n">
+      <c r="A142" s="6" t="n">
         <v>45944</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="1" t="n">
@@ -5748,10 +5746,10 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7" t="n">
+      <c r="A143" s="6" t="n">
         <v>45944</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C143" s="1" t="n">
@@ -5786,10 +5784,10 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7" t="n">
+      <c r="A144" s="6" t="n">
         <v>45950</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C144" s="1" t="n">
@@ -5824,10 +5822,10 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7" t="n">
+      <c r="A145" s="6" t="n">
         <v>45950</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C145" s="1" t="n">
@@ -5862,10 +5860,10 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7" t="n">
+      <c r="A146" s="6" t="n">
         <v>45958</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="1" t="n">
@@ -5900,10 +5898,10 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7" t="n">
+      <c r="A147" s="6" t="n">
         <v>45958</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C147" s="1" t="n">
@@ -5938,10 +5936,10 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7" t="n">
+      <c r="A148" s="6" t="n">
         <v>45959</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C148" s="1" t="n">
@@ -5976,10 +5974,10 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7" t="n">
+      <c r="A149" s="6" t="n">
         <v>45959</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C149" s="1" t="n">
@@ -6014,10 +6012,10 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="7" t="n">
+      <c r="A150" s="6" t="n">
         <v>45960</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C150" s="1" t="n">
@@ -6052,10 +6050,10 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7" t="n">
+      <c r="A151" s="6" t="n">
         <v>45960</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C151" s="1" t="n">
@@ -6090,10 +6088,10 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="7" t="n">
+      <c r="A152" s="6" t="n">
         <v>45961</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B152" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C152" s="1" t="n">
@@ -6128,10 +6126,10 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7" t="n">
+      <c r="A153" s="6" t="n">
         <v>45961</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C153" s="1" t="n">
@@ -6166,10 +6164,10 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="7" t="n">
+      <c r="A154" s="6" t="n">
         <v>45965</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C154" s="1" t="n">
@@ -6204,10 +6202,10 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7" t="n">
+      <c r="A155" s="6" t="n">
         <v>45965</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C155" s="1" t="n">
@@ -6242,10 +6240,10 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="7" t="n">
+      <c r="A156" s="6" t="n">
         <v>45973</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B156" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C156" s="1" t="n">
@@ -6280,10 +6278,10 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7" t="n">
+      <c r="A157" s="6" t="n">
         <v>45973</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C157" s="1" t="n">
@@ -6318,10 +6316,10 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="7" t="n">
+      <c r="A158" s="6" t="n">
         <v>45974</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C158" s="1" t="n">
@@ -6356,10 +6354,10 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7" t="n">
+      <c r="A159" s="6" t="n">
         <v>45974</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C159" s="1" t="n">
@@ -6394,10 +6392,10 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="7" t="n">
+      <c r="A160" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B160" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C160" s="1" t="n">
@@ -6432,10 +6430,10 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7" t="n">
+      <c r="A161" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C161" s="1" t="n">
@@ -6470,10 +6468,10 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7" t="n">
+      <c r="A162" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C162" s="1" t="n">
@@ -6508,10 +6506,10 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7" t="n">
+      <c r="A163" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C163" s="1" t="n">
@@ -6546,10 +6544,10 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="7" t="n">
+      <c r="A164" s="6" t="n">
         <v>45980</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C164" s="1" t="n">
@@ -6584,10 +6582,10 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7" t="n">
+      <c r="A165" s="6" t="n">
         <v>45980</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C165" s="1" t="n">
@@ -6622,10 +6620,10 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="7" t="n">
+      <c r="A166" s="6" t="n">
         <v>45981</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C166" s="1" t="n">
@@ -6660,10 +6658,10 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="n">
+      <c r="A167" s="6" t="n">
         <v>45981</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C167" s="1" t="n">
@@ -6698,10 +6696,10 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="n">
+      <c r="A168" s="6" t="n">
         <v>45982</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B168" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="1" t="n">
@@ -6736,10 +6734,10 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="n">
+      <c r="A169" s="6" t="n">
         <v>45982</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C169" s="1" t="n">
@@ -6774,10 +6772,10 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7" t="n">
+      <c r="A170" s="6" t="n">
         <v>45990</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B170" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C170" s="1" t="n">
@@ -6812,10 +6810,10 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="n">
+      <c r="A171" s="6" t="n">
         <v>45990</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C171" s="1" t="n">
@@ -6850,10 +6848,10 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7" t="n">
+      <c r="A172" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B172" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="1" t="n">
@@ -6888,10 +6886,10 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="n">
+      <c r="A173" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C173" s="1" t="n">
@@ -6926,10 +6924,10 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7" t="n">
+      <c r="A174" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B174" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="1" t="n">
@@ -6964,10 +6962,10 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="n">
+      <c r="A175" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C175" s="1" t="n">
@@ -7002,10 +7000,10 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7" t="n">
+      <c r="A176" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B176" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="1" t="n">
@@ -7040,10 +7038,10 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="n">
+      <c r="A177" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C177" s="1" t="n">
@@ -7078,10 +7076,10 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7" t="n">
+      <c r="A178" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="1" t="n">
@@ -7116,10 +7114,10 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="n">
+      <c r="A179" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C179" s="1" t="n">
@@ -7154,10 +7152,10 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7" t="n">
+      <c r="A180" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B180" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="1" t="n">
@@ -7192,10 +7190,10 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="n">
+      <c r="A181" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C181" s="1" t="n">
@@ -7230,10 +7228,10 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7" t="n">
+      <c r="A182" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C182" s="1" t="n">
@@ -7268,10 +7266,10 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="n">
+      <c r="A183" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C183" s="1" t="n">
@@ -7306,10 +7304,10 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7" t="n">
+      <c r="A184" s="6" t="n">
         <v>46010</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B184" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C184" s="1" t="n">
@@ -7344,10 +7342,10 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="n">
+      <c r="A185" s="6" t="n">
         <v>46010</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C185" s="1" t="n">
@@ -7382,10 +7380,10 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7" t="n">
+      <c r="A186" s="6" t="n">
         <v>46029</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C186" s="1" t="n">
@@ -7420,10 +7418,10 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="n">
+      <c r="A187" s="6" t="n">
         <v>46029</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C187" s="1" t="n">
@@ -7458,108 +7456,108 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7" t="n">
+      <c r="A188" s="6" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F188" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H188" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="6" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F189" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H189" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="K189" s="3" t="n">
+        <v>-88</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="6" t="n">
         <v>46031</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C188" s="1" t="n">
+      <c r="B190" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D188" s="1" t="n">
+      <c r="D190" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="E188" s="1" t="n">
+      <c r="E190" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="F188" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="G188" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H188" s="1" t="n">
-        <v>1478</v>
-      </c>
-      <c r="I188" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J188" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7" t="n">
-        <v>46031</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C189" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E189" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="F189" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H189" s="1" t="n">
-        <v>1478</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J189" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="K189" s="3" t="n">
-        <v>-69</v>
-      </c>
-      <c r="L189" s="3" t="n">
-        <v>-28</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="n">
-        <v>46035</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C190" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="E190" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="F190" s="1" t="n">
         <v>29</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>1222</v>
+        <v>1478</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J190" s="3" t="n">
         <v>0</v>
@@ -7572,67 +7570,67 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7" t="n">
+      <c r="A191" s="6" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="F191" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H191" s="1" t="n">
+        <v>1478</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>-69</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="6" t="n">
         <v>46035</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E191" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F191" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H191" s="1" t="n">
-        <v>1222</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J191" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="K191" s="3" t="n">
-        <v>-83</v>
-      </c>
-      <c r="L191" s="3" t="n">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7" t="n">
-        <v>46039</v>
-      </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D192" s="1" t="n">
         <v>86</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>1624</v>
+        <v>1222</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>17</v>
@@ -7648,117 +7646,269 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7" t="n">
+      <c r="A193" s="6" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F193" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H193" s="1" t="n">
+        <v>1222</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="6" t="n">
         <v>46039</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C193" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E193" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F193" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H193" s="1" t="n">
-        <v>1624</v>
-      </c>
-      <c r="I193" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J193" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="K193" s="3" t="n">
-        <v>-91</v>
-      </c>
-      <c r="L193" s="3" t="n">
-        <v>-28</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7" t="n">
-        <v>46041</v>
-      </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D194" s="1" t="n">
         <v>86</v>
       </c>
       <c r="E194" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F194" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>1624</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="6" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F195" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H195" s="1" t="n">
+        <v>1624</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>-91</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="6" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E196" s="1" t="n">
         <v>9.6</v>
       </c>
-      <c r="F194" s="1" t="n">
+      <c r="F196" s="1" t="n">
         <v>32.7</v>
       </c>
-      <c r="G194" s="2" t="s">
+      <c r="G196" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H194" s="1" t="n">
+      <c r="H196" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="I194" s="1" t="s">
+      <c r="I196" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7" t="n">
+      <c r="J196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="6" t="n">
         <v>46041</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C195" s="1" t="n">
+      <c r="B197" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="D195" s="1" t="n">
+      <c r="D197" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E195" s="1" t="n">
+      <c r="E197" s="1" t="n">
         <v>87.7</v>
       </c>
-      <c r="F195" s="1" t="n">
+      <c r="F197" s="1" t="n">
         <v>58.9</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="G197" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H195" s="1" t="n">
+      <c r="H197" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="I195" s="1" t="s">
+      <c r="I197" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J195" s="3" t="n">
+      <c r="J197" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="K195" s="3" t="n">
+      <c r="K197" s="3" t="n">
         <v>-78.1</v>
       </c>
-      <c r="L195" s="3" t="n">
+      <c r="L197" s="3" t="n">
         <v>-26.2</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F198" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H198" s="1" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F199" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H199" s="1" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="K199" s="3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="L199" s="3" t="n">
+        <v>-33</v>
       </c>
     </row>
   </sheetData>

--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -353,7 +353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L207"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -7837,31 +7837,31 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="n">
-        <v>46048</v>
+        <v>46045</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F198" s="1" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>1029</v>
+        <v>1005</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J198" s="3" t="n">
         <v>0</v>
@@ -7875,39 +7875,343 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="6" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F199" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H199" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K199" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="L199" s="3" t="n">
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="6" t="n">
         <v>46048</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C199" s="1" t="n">
+      <c r="B200" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F200" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H200" s="1" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="6" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="D199" s="1" t="n">
+      <c r="D201" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E199" s="1" t="n">
+      <c r="E201" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F199" s="1" t="n">
+      <c r="F201" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="G199" s="2" t="s">
+      <c r="G201" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H199" s="1" t="n">
+      <c r="H201" s="1" t="n">
         <v>1029</v>
       </c>
-      <c r="I199" s="1" t="s">
+      <c r="I201" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J199" s="3" t="n">
+      <c r="J201" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="K199" s="3" t="n">
+      <c r="K201" s="3" t="n">
         <v>-84</v>
       </c>
-      <c r="L199" s="3" t="n">
+      <c r="L201" s="3" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="6" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="E202" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F202" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H202" s="1" t="n">
+        <v>1052</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="6" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E203" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="F203" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H203" s="1" t="n">
+        <v>1052</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K203" s="3" t="n">
+        <v>-92</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="6" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E204" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" s="1" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="6" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E205" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F205" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H205" s="1" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K205" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="E206" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F206" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H206" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F207" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H207" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="K207" s="3" t="n">
+        <v>-88</v>
+      </c>
+      <c r="L207" s="3" t="n">
         <v>-33</v>
       </c>
     </row>

--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t xml:space="preserve">Clarity Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focaldata</t>
   </si>
 </sst>
 </file>
@@ -353,7 +356,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L209"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -8141,7 +8144,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>12</v>
@@ -8179,7 +8182,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>15</v>
@@ -8213,6 +8216,82 @@
       </c>
       <c r="L207" s="3" t="n">
         <v>-33</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F208" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H208" s="1" t="n">
+        <v>1148</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F209" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H209" s="1" t="n">
+        <v>1148</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K209" s="3" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>-39</v>
       </c>
     </row>
   </sheetData>

--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -356,7 +356,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L215"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -8292,6 +8292,234 @@
       </c>
       <c r="L209" s="3" t="n">
         <v>-39</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="6" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="E210" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F210" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H210" s="1" t="n">
+        <v>2496</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="6" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E211" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F211" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H211" s="1" t="n">
+        <v>2496</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="K211" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="6" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F212" s="1" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H212" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="6" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>92.6</v>
+      </c>
+      <c r="F213" s="1" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H213" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K213" s="3" t="n">
+        <v>-87.3</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="6" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F214" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H214" s="1" t="n">
+        <v>2381</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="6" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E215" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F215" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H215" s="1" t="n">
+        <v>2381</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="K215" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L215" s="3" t="n">
+        <v>-38</v>
       </c>
     </row>
   </sheetData>

--- a/data/trumptracker.xlsx
+++ b/data/trumptracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -356,7 +356,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -8520,6 +8520,82 @@
       </c>
       <c r="L215" s="3" t="n">
         <v>-38</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="6" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="E216" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F216" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H216" s="1" t="n">
+        <v>1456</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="6" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="F217" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H217" s="1" t="n">
+        <v>1456</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="K217" s="3" t="n">
+        <v>-75</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>-34</v>
       </c>
     </row>
   </sheetData>
